--- a/data/trans_orig/IBSE_100-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IBSE_100-Habitat-trans_orig.xlsx
@@ -548,17 +548,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>76,64</t>
+          <t>76,62</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>72,9</t>
+          <t>72,99</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>74,72</t>
+          <t>74,76</t>
         </is>
       </c>
     </row>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>74,97; 78,58</t>
+          <t>74,72; 78,28</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>71,66; 74,12</t>
+          <t>71,72; 74,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>73,76; 75,91</t>
+          <t>73,75; 75,76</t>
         </is>
       </c>
     </row>
@@ -598,17 +598,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>80,71</t>
+          <t>78,78</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>73,85</t>
+          <t>73,73</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>77,67</t>
+          <t>76,24</t>
         </is>
       </c>
     </row>
@@ -621,17 +621,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>78,39; 84,21</t>
+          <t>77,63; 79,99</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>72,86; 75,04</t>
+          <t>72,58; 74,82</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>76,04; 81,5</t>
+          <t>75,35; 77,1</t>
         </is>
       </c>
     </row>
@@ -653,12 +653,12 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>77,65</t>
+          <t>76,77</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>78,56</t>
+          <t>78,26</t>
         </is>
       </c>
     </row>
@@ -671,17 +671,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>78,46; 81,19</t>
+          <t>78,46; 81,11</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>76,02; 79,33</t>
+          <t>75,47; 77,94</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>77,59; 79,61</t>
+          <t>77,26; 79,06</t>
         </is>
       </c>
     </row>
@@ -698,17 +698,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>76,85</t>
+          <t>76,72</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>73,56</t>
+          <t>72,83</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>75,07</t>
+          <t>74,66</t>
         </is>
       </c>
     </row>
@@ -721,17 +721,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>75,54; 77,98</t>
+          <t>75,43; 77,91</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>72,26; 75,6</t>
+          <t>71,82; 73,86</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>74,2; 76,24</t>
+          <t>73,79; 75,39</t>
         </is>
       </c>
     </row>
@@ -748,17 +748,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>78,74</t>
+          <t>78,01</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>74,56</t>
+          <t>73,98</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>76,6</t>
+          <t>75,94</t>
         </is>
       </c>
     </row>
@@ -771,17 +771,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>77,71; 80,8</t>
+          <t>77,33; 78,63</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>73,81; 75,62</t>
+          <t>73,45; 74,58</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>75,91; 78,06</t>
+          <t>75,47; 76,37</t>
         </is>
       </c>
     </row>
